--- a/月報表.xlsx
+++ b/月報表.xlsx
@@ -26142,319 +26142,319 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>20</v>
+      </c>
+      <c r="C38" t="n">
         <v>10</v>
-      </c>
-      <c r="C38" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DUP01I</t>
+          <t>DYN01I</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DYN01I</t>
+          <t>EPH01I</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C40" t="n">
-        <v>137</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EPH01I</t>
+          <t>ERA01I</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ERA01I</t>
+          <t>EVE01I</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EVE01I</t>
+          <t>FAS01I</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FAS01I</t>
+          <t>FEB02I</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FEB02I</t>
+          <t>FIL03I</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FIL03I</t>
+          <t>FLE02I</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>60</v>
+        <v>2232</v>
       </c>
       <c r="C46" t="n">
-        <v>18</v>
+        <v>496</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FLE02I</t>
+          <t>FLU11I</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2232</v>
+        <v>3200</v>
       </c>
       <c r="C47" t="n">
-        <v>496</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLU11I</t>
+          <t>FOY01I</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3200</v>
+        <v>150</v>
       </c>
       <c r="C48" t="n">
-        <v>1440</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FOY01I</t>
+          <t>FUL03I</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FUL03I</t>
+          <t>FUR02I</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14</v>
+        <v>1200</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FUR02I</t>
+          <t>GLU04I</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="C51" t="n">
-        <v>1728</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GLU04I</t>
+          <t>GLU30I</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C52" t="n">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GLU30I</t>
+          <t>GLY02I</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="C53" t="n">
-        <v>116</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GLY02I</t>
+          <t>GLY11I</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="C54" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GLY11I</t>
+          <t>HAL01I</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="C55" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HAL01I</t>
+          <t>HEM11I</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>20</v>
+        <v>1600</v>
       </c>
       <c r="C56" t="n">
-        <v>24</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HEM11I</t>
+          <t>HEP16I</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="C57" t="n">
-        <v>456</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HEP16I</t>
+          <t>HUM08I</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HUM08I</t>
+          <t>INV01I</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INV01I</t>
+          <t>INV02I</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>68</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>INV02I</t>
+          <t>INV03I</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C61" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INV03I</t>
+          <t>IOP05I</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
         <v>4</v>
@@ -26463,4589 +26463,4576 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IOP05I</t>
+          <t>KEP01I</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KEP01I</t>
+          <t>LAC02I</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="C64" t="n">
-        <v>-69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LAC02I</t>
+          <t>LID03I</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C65" t="n">
-        <v>26</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LID03I</t>
+          <t>LID04I</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C66" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LID04I</t>
+          <t>LOW01I</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LOW01I</t>
+          <t>LUM03I</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LUM03I</t>
+          <t>MAG03I</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MAG03I</t>
+          <t>MAN01I</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="C70" t="n">
-        <v>225</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MAN01I</t>
+          <t>MAR01I</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="C71" t="n">
-        <v>-15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MAR01I</t>
+          <t>MEN01I</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>120</v>
+        <v>410</v>
       </c>
       <c r="C72" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MEN01I</t>
+          <t>MEP02I</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MEP02I</t>
+          <t>MET02I</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1000</v>
       </c>
       <c r="C74" t="n">
-        <v>1185</v>
+        <v>671</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MET02I</t>
+          <t>MIN06I</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C75" t="n">
-        <v>671</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MIN06I</t>
+          <t>MYC01I</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MYC01I</t>
+          <t>NAL02I</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NAL02I</t>
+          <t>NEP01I</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>-1146</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NEP01I</t>
+          <t>NIM03I</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="C79" t="n">
-        <v>-1146</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NIM03I</t>
+          <t>NIV01I</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="C80" t="n">
-        <v>101</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NIV01I</t>
+          <t>NOO02I</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C81" t="n">
-        <v>31</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NOO02I</t>
+          <t>NOR04I</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>100</v>
+        <v>720</v>
       </c>
       <c r="C82" t="n">
-        <v>115</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NOR04I</t>
+          <t>NUC02I</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>720</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>294</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NUC02I</t>
+          <t>PAN02I</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>360</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>666</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PAN02I</t>
+          <t>PG201I</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>360</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>666</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PG201I</t>
+          <t>PHY01I</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>800</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>382</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PHY01I</t>
+          <t>PIT02I</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>382</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PIT02I</t>
+          <t>PRI04I</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>110</v>
       </c>
       <c r="C88" t="n">
-        <v>78</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PRI04I</t>
+          <t>PRI05I</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C89" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PRI05I</t>
+          <t>PRO02I</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>60</v>
+        <v>2000</v>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>758</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRO02I</t>
+          <t>PRO05I</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="C91" t="n">
-        <v>758</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PRO05I</t>
+          <t>PRO14I</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="C92" t="n">
-        <v>221</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PRO14I</t>
+          <t>PYR04I</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="C93" t="n">
-        <v>69</v>
+        <v>284</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PYR04I</t>
+          <t>RAP04I</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="C94" t="n">
-        <v>284</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RAP04I</t>
+          <t>RIN12I</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RIN12I</t>
+          <t>RIN13I</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RIN13I</t>
+          <t>ROS01I</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="C97" t="n">
-        <v>48</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ROS01I</t>
+          <t>SAB01I</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2000</v>
+        <v>640</v>
       </c>
       <c r="C98" t="n">
-        <v>1305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SAB01I</t>
+          <t>SAN04I</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>640</v>
+        <v>160</v>
       </c>
       <c r="C99" t="n">
-        <v>318</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAN04I</t>
+          <t>SET02I</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="C100" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SET02I</t>
+          <t>SEV01I</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C101" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SEV01I</t>
+          <t>SMO04I</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="C102" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SMO04I</t>
+          <t>SOD12I</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SOD12I</t>
+          <t>SOD15I</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SOD15I</t>
+          <t>SOL02I</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>96</v>
+        <v>400</v>
       </c>
       <c r="C105" t="n">
-        <v>19</v>
+        <v>161</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SOL02I</t>
+          <t>SOL03I</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="C106" t="n">
-        <v>161</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SOL03I</t>
+          <t>SOL04I</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="C107" t="n">
-        <v>32</v>
+        <v>471</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SOL04I</t>
+          <t>STA01I</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="C108" t="n">
-        <v>471</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STA01I</t>
+          <t>STR05I</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="C109" t="n">
-        <v>1613</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STR05I</t>
+          <t>SUB01I</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="C110" t="n">
-        <v>171</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SUB01I</t>
+          <t>SUN01I</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>1377</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SUN01I</t>
+          <t>TAI03I</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C112" t="n">
-        <v>141</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TAI03I</t>
+          <t>TAI05I</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="C113" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TAI05I</t>
+          <t>TAR02I</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="C114" t="n">
-        <v>83</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TAR02I</t>
+          <t>TAT03I</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>72</v>
+        <v>480</v>
       </c>
       <c r="C115" t="n">
-        <v>-11</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TAT03I</t>
+          <t>TEI01I</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="C116" t="n">
-        <v>364</v>
+        <v>449</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TEI01I</t>
+          <t>TIG01I</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="C117" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TIG01I</t>
+          <t>TYG01I</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TYG01I</t>
+          <t>ULC01I</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="C119" t="n">
-        <v>43</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ULC01I</t>
+          <t>URO07I</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C120" t="n">
-        <v>185</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>URO07I</t>
+          <t>USO01I</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C121" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>USO01I</t>
+          <t>VAG01I</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="C122" t="n">
-        <v>28</v>
+        <v>860</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VAG01I</t>
+          <t>VAN04I</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="C123" t="n">
-        <v>860</v>
+        <v>85</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VAN04I</t>
+          <t>VFE01I</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C124" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VFE01I</t>
+          <t>VIM01I</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="C125" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>VIM01I</t>
+          <t>VIT01I</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>120</v>
+        <v>2400</v>
       </c>
       <c r="C126" t="n">
-        <v>26</v>
+        <v>797</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VIT01I</t>
+          <t>VOL01I</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2400</v>
+        <v>60</v>
       </c>
       <c r="C127" t="n">
-        <v>797</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VOL01I</t>
+          <t>XOL01I</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>XOL01I</t>
+          <t>ZAV02I</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ZAV02I</t>
+          <t>ZIE01I</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ZIE01I</t>
+          <t>ZIN04I</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ZIN04I</t>
+          <t>ZOL02I</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>390</v>
+        <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZOL02I</t>
+          <t>ZOV01I</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ZOV01I</t>
+          <t>ZYP02I</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C134" t="n">
-        <v>128</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ZYP02I</t>
+          <t>ACA01O</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>627</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ACA01O</t>
+          <t>ACE04O</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>1000</v>
       </c>
       <c r="C136" t="n">
-        <v>627</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ACE04O</t>
+          <t>ACT01O</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="C137" t="n">
-        <v>223</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ACT01O</t>
+          <t>ACT02O</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>90</v>
+        <v>1680</v>
       </c>
       <c r="C138" t="n">
-        <v>40</v>
+        <v>549</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ACT02O</t>
+          <t>ACT06O</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1680</v>
+        <v>14000</v>
       </c>
       <c r="C139" t="n">
-        <v>549</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ACT06O</t>
+          <t>ACY02O</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>14000</v>
+        <v>200</v>
       </c>
       <c r="C140" t="n">
-        <v>4698</v>
+        <v>153</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ACY02O</t>
+          <t>ADV01O</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="C141" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADV01O</t>
+          <t>AKY01O</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AKY01O</t>
+          <t>ALG01O</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>60</v>
+        <v>1680</v>
       </c>
       <c r="C143" t="n">
-        <v>12</v>
+        <v>477</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALG01O</t>
+          <t>ALI01O</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1680</v>
+        <v>2400</v>
       </c>
       <c r="C144" t="n">
-        <v>477</v>
+        <v>746</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ALI01O</t>
+          <t>ALL02O</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="C145" t="n">
-        <v>746</v>
+        <v>771</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ALL02O</t>
+          <t>AMA02O</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3200</v>
+        <v>420</v>
       </c>
       <c r="C146" t="n">
-        <v>771</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AMA02O</t>
+          <t>AMA03O</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="C147" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AMA03O</t>
+          <t>ANT06O</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C148" t="n">
-        <v>166</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ANT06O</t>
+          <t>ARI03O</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1000</v>
+        <v>336</v>
       </c>
       <c r="C149" t="n">
-        <v>336</v>
+        <v>-134</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ARI03O</t>
+          <t>AVE01O</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>336</v>
+        <v>50</v>
       </c>
       <c r="C150" t="n">
-        <v>-134</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AVE01O</t>
+          <t>AVO01O</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>50</v>
+        <v>360</v>
       </c>
       <c r="C151" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AVO01O</t>
+          <t>BAK01O</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="C152" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BAK01O</t>
+          <t>BAR02O</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="C153" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BAR02O</t>
+          <t>BEF01O</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>240</v>
+        <v>1500</v>
       </c>
       <c r="C154" t="n">
-        <v>122</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BEF01O</t>
+          <t>BET01O</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1500</v>
+        <v>252</v>
       </c>
       <c r="C155" t="n">
-        <v>473</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BET01O</t>
+          <t>BET02O</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>252</v>
       </c>
       <c r="C156" t="n">
-        <v>21</v>
+        <v>131</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BET02O</t>
+          <t>BIO02O</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>252</v>
+        <v>1680</v>
       </c>
       <c r="C157" t="n">
-        <v>131</v>
+        <v>454</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BIO02O</t>
+          <t>BIP01O</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1680</v>
+        <v>2000</v>
       </c>
       <c r="C158" t="n">
-        <v>454</v>
+        <v>878</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BIP01O</t>
+          <t>BIS04O</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C159" t="n">
-        <v>878</v>
+        <v>923</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BIS04O</t>
+          <t>BLO01O</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1000</v>
+        <v>1680</v>
       </c>
       <c r="C160" t="n">
-        <v>923</v>
+        <v>418</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BLO01O</t>
+          <t>BLO02O</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1680</v>
+        <v>3000</v>
       </c>
       <c r="C161" t="n">
-        <v>418</v>
+        <v>655</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BLO02O</t>
+          <t>BLO03O</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3000</v>
+        <v>280</v>
       </c>
       <c r="C162" t="n">
-        <v>655</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BLO03O</t>
+          <t>BOK01O</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>280</v>
+        <v>4900</v>
       </c>
       <c r="C163" t="n">
-        <v>44</v>
+        <v>986</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BOK01O</t>
+          <t>BOW01O</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>4900</v>
+        <v>70</v>
       </c>
       <c r="C164" t="n">
-        <v>986</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BOW01O</t>
+          <t>BRI01O</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>70</v>
+        <v>448</v>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BRI01O</t>
+          <t>BRO02O</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>448</v>
+        <v>5000</v>
       </c>
       <c r="C166" t="n">
-        <v>179</v>
+        <v>827</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BRO02O</t>
+          <t>CAR04O</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="C167" t="n">
-        <v>827</v>
+        <v>738</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CAR04O</t>
+          <t>CEF01O</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C168" t="n">
-        <v>738</v>
+        <v>97</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CEF01O</t>
+          <t>CEL04O</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="C169" t="n">
-        <v>97</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CEL04O</t>
+          <t>CEL05O</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1120</v>
+        <v>700</v>
       </c>
       <c r="C170" t="n">
-        <v>-105</v>
+        <v>191</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CEL05O</t>
+          <t>CEP05O</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>700</v>
+        <v>6000</v>
       </c>
       <c r="C171" t="n">
-        <v>191</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CEP05O</t>
+          <t>CEX01O</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="C172" t="n">
-        <v>2935</v>
+        <v>998</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CEX01O</t>
+          <t>CIN02O</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4200</v>
+        <v>1500</v>
       </c>
       <c r="C173" t="n">
-        <v>998</v>
+        <v>722</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CIN02O</t>
+          <t>CIT01O</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1500</v>
+        <v>560</v>
       </c>
       <c r="C174" t="n">
-        <v>722</v>
+        <v>239</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CIT01O</t>
+          <t>COF01O</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="C175" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>COF01O</t>
+          <t>COL01O</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C176" t="n">
-        <v>194</v>
+        <v>241</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>COL01O</t>
+          <t>COM05O</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="C177" t="n">
-        <v>241</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>COM05O</t>
+          <t>CON01O</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6000</v>
+        <v>1960</v>
       </c>
       <c r="C178" t="n">
-        <v>1811</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CON01O</t>
+          <t>CON06O</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1960</v>
+        <v>1800</v>
       </c>
       <c r="C179" t="n">
-        <v>1172</v>
+        <v>791</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CON06O</t>
+          <t>CON08O</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1800</v>
+        <v>5220</v>
       </c>
       <c r="C180" t="n">
-        <v>791</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CON08O</t>
+          <t>CON10O</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5220</v>
+        <v>200</v>
       </c>
       <c r="C181" t="n">
-        <v>1546</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CON10O</t>
+          <t>COR02O</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>200</v>
+        <v>448</v>
       </c>
       <c r="C182" t="n">
-        <v>205</v>
+        <v>331</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>COR02O</t>
+          <t>COR05O</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>448</v>
+        <v>1620</v>
       </c>
       <c r="C183" t="n">
-        <v>331</v>
+        <v>682</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>COR05O</t>
+          <t>CRA02O</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1620</v>
+        <v>200</v>
       </c>
       <c r="C184" t="n">
-        <v>682</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CRA02O</t>
+          <t>CRE01O</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>200</v>
+        <v>1512</v>
       </c>
       <c r="C185" t="n">
-        <v>173</v>
+        <v>458</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CRE01O</t>
+          <t>CUR01O</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1512</v>
+        <v>2240</v>
       </c>
       <c r="C186" t="n">
-        <v>458</v>
+        <v>379</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CUR01O</t>
+          <t>CYT02O</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2240</v>
+        <v>90</v>
       </c>
       <c r="C187" t="n">
-        <v>379</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CYT02O</t>
+          <t>DAF01O</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>90</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DAF01O</t>
+          <t>DAM01O</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="C189" t="n">
-        <v>74</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DAM01O</t>
+          <t>DAY01O</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2000</v>
+        <v>112</v>
       </c>
       <c r="C190" t="n">
-        <v>1571</v>
+        <v>53</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DAY01O</t>
+          <t>DEL03O</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>112</v>
+        <v>1000</v>
       </c>
       <c r="C191" t="n">
-        <v>53</v>
+        <v>390</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DEL03O</t>
+          <t>DEP01O</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C192" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DEP01O</t>
+          <t>DEP03O</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>800</v>
+        <v>24000</v>
       </c>
       <c r="C193" t="n">
-        <v>268</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DEP03O</t>
+          <t>DIA04O</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>24000</v>
+        <v>300</v>
       </c>
       <c r="C194" t="n">
-        <v>3062</v>
+        <v>128</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DIA04O</t>
+          <t>DIM04O</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="C195" t="n">
-        <v>128</v>
+        <v>792</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DIM04O</t>
+          <t>DIO01O</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1000</v>
+        <v>1344</v>
       </c>
       <c r="C196" t="n">
-        <v>792</v>
+        <v>876</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DIO01O</t>
+          <t>DIP03O</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1344</v>
+        <v>2000</v>
       </c>
       <c r="C197" t="n">
-        <v>876</v>
+        <v>540</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DIP03O</t>
+          <t>DOR04O</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C198" t="n">
-        <v>540</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DOR04O</t>
+          <t>DOS01O</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="C199" t="n">
-        <v>223</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DOS01O</t>
+          <t>DOX02O</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="C200" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DOX02O</t>
+          <t>DOX03O</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="C201" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DOX03O</t>
+          <t>DUX01O</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="C202" t="n">
-        <v>115</v>
+        <v>190</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DUX01O</t>
+          <t>ECT02O</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>840</v>
+        <v>400</v>
       </c>
       <c r="C203" t="n">
-        <v>190</v>
+        <v>597</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ECT02O</t>
+          <t>EDA01O</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>400</v>
+        <v>224</v>
       </c>
       <c r="C204" t="n">
-        <v>597</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>EDA01O</t>
+          <t>EFE02O</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="C205" t="n">
-        <v>26</v>
+        <v>184</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>EFE02O</t>
+          <t>EFI02O</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>280</v>
+        <v>1120</v>
       </c>
       <c r="C206" t="n">
-        <v>184</v>
+        <v>385</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EFI02O</t>
+          <t>ELI02O</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1120</v>
+        <v>336</v>
       </c>
       <c r="C207" t="n">
-        <v>385</v>
+        <v>122</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ELI02O</t>
+          <t>ELI03O</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>336</v>
+        <v>672</v>
       </c>
       <c r="C208" t="n">
-        <v>122</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ELI03O</t>
+          <t>ELT01O</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>672</v>
+        <v>2000</v>
       </c>
       <c r="C209" t="n">
-        <v>25</v>
+        <v>737</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ELT01O</t>
+          <t>EME02O</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2000</v>
+        <v>90</v>
       </c>
       <c r="C210" t="n">
-        <v>737</v>
+        <v>42</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EME02O</t>
+          <t>EME03O</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C211" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EME03O</t>
+          <t>ENT01O</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="C212" t="n">
-        <v>29</v>
+        <v>389</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ENT01O</t>
+          <t>ENT02O</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>352</v>
+        <v>224</v>
       </c>
       <c r="C213" t="n">
-        <v>389</v>
+        <v>50</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ENT02O</t>
+          <t>ENT03O</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>224</v>
+        <v>840</v>
       </c>
       <c r="C214" t="n">
-        <v>50</v>
+        <v>237</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ENT03O</t>
+          <t>ETU01O</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>840</v>
+        <v>500</v>
       </c>
       <c r="C215" t="n">
-        <v>237</v>
+        <v>197</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ETU01O</t>
+          <t>EUR02O</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="C216" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EUR02O</t>
+          <t>EVI01O</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1400</v>
+        <v>28</v>
       </c>
       <c r="C217" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EVI01O</t>
+          <t>EVO01O</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="C218" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EVO01O</t>
+          <t>EXE04O</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="C219" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EXE04O</t>
+          <t>EXF01O</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>84</v>
+        <v>2016</v>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>-141</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>EXF01O</t>
+          <t>EZE01O</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2016</v>
+        <v>300</v>
       </c>
       <c r="C221" t="n">
-        <v>-141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EZE01O</t>
+          <t>FAM01O</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="C222" t="n">
-        <v>92</v>
+        <v>-492</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FAM01O</t>
+          <t>FAM02O</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="C223" t="n">
-        <v>-492</v>
+        <v>32</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FAM02O</t>
+          <t>FEB01O</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>30</v>
+        <v>840</v>
       </c>
       <c r="C224" t="n">
-        <v>32</v>
+        <v>209</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FEB01O</t>
+          <t>FEM01O</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>840</v>
+        <v>30</v>
       </c>
       <c r="C225" t="n">
-        <v>209</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FEM01O</t>
+          <t>FLU04O</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="C226" t="n">
-        <v>22</v>
+        <v>219</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FLU04O</t>
+          <t>FOL02O</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C227" t="n">
-        <v>219</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FOL02O</t>
+          <t>FOR01O</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="C228" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FOR01O</t>
+          <t>FUS01O</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>336</v>
+        <v>200</v>
       </c>
       <c r="C229" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FUS01O</t>
+          <t>GAL02O</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="C230" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GAL02O</t>
+          <t>GAS07O</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>112</v>
+        <v>15000</v>
       </c>
       <c r="C231" t="n">
-        <v>76</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GAS07O</t>
+          <t>GEN01O</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="C232" t="n">
-        <v>4087</v>
+        <v>359</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GEN01O</t>
+          <t>GEO02O</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>359</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>GEO02O</t>
+          <t>GIK01O</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C234" t="n">
-        <v>-90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GIK01O</t>
+          <t>GLU07O</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>120</v>
+        <v>3360</v>
       </c>
       <c r="C235" t="n">
-        <v>33</v>
+        <v>792</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GLU07O</t>
+          <t>GLY01O</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>3360</v>
+        <v>1000</v>
       </c>
       <c r="C236" t="n">
-        <v>792</v>
+        <v>247</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>GLY01O</t>
+          <t>GLY02O</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="C237" t="n">
-        <v>247</v>
+        <v>36</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GLY02O</t>
+          <t>HAR04O</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="C238" t="n">
-        <v>36</v>
+        <v>291</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HAR04O</t>
+          <t>HYD04O</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="C239" t="n">
-        <v>291</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HYD04O</t>
+          <t>INS01O</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C240" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>INS01O</t>
+          <t>INV01O</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>190</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>INV01O</t>
+          <t>INV02O</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C242" t="n">
-        <v>190</v>
+        <v>113</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>INV02O</t>
+          <t>ISO09O</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>180</v>
+        <v>1600</v>
       </c>
       <c r="C243" t="n">
-        <v>113</v>
+        <v>809</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ISO09O</t>
+          <t>JAR01O</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="C244" t="n">
-        <v>809</v>
+        <v>-386</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>JAR01O</t>
+          <t>JAR02O</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="C245" t="n">
-        <v>-386</v>
+        <v>73</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>JAR02O</t>
+          <t>KCI01O</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1080</v>
+        <v>25</v>
       </c>
       <c r="C246" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>KCI01O</t>
+          <t>KEP01O</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="C247" t="n">
-        <v>22</v>
+        <v>546</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>KEP01O</t>
+          <t>KET04O</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="C248" t="n">
-        <v>546</v>
+        <v>364</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>KET04O</t>
+          <t>KIS01O</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>300</v>
+        <v>252</v>
       </c>
       <c r="C249" t="n">
-        <v>364</v>
+        <v>57</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>KIS01O</t>
+          <t>LAN02O</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>252</v>
+        <v>1000</v>
       </c>
       <c r="C250" t="n">
-        <v>57</v>
+        <v>164</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>LAN02O</t>
+          <t>LAT01O</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C251" t="n">
-        <v>164</v>
+        <v>261</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>LAT01O</t>
+          <t>LEU05O</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="C252" t="n">
-        <v>261</v>
+        <v>12</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>LEU05O</t>
+          <t>LIC01O</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="C253" t="n">
-        <v>12</v>
+        <v>341</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LIC01O</t>
+          <t>LIP13O</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>600</v>
+        <v>3360</v>
       </c>
       <c r="C254" t="n">
-        <v>341</v>
+        <v>714</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LIP13O</t>
+          <t>LIP14O</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>3360</v>
+        <v>660</v>
       </c>
       <c r="C255" t="n">
-        <v>714</v>
+        <v>229</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LIP14O</t>
+          <t>LIV02O</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>660</v>
+        <v>1680</v>
       </c>
       <c r="C256" t="n">
-        <v>229</v>
+        <v>312</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>LIV02O</t>
+          <t>LIX03O</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1680</v>
+        <v>420</v>
       </c>
       <c r="C257" t="n">
-        <v>312</v>
+        <v>42</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>LIX03O</t>
+          <t>LON05O</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="C258" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>LON05O</t>
+          <t>LUC01O</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="C259" t="n">
-        <v>4</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>LUC01O</t>
+          <t>LYN01O</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>5000</v>
+        <v>336</v>
       </c>
       <c r="C260" t="n">
-        <v>1606</v>
+        <v>113</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>LYN01O</t>
+          <t>LYR01O</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>336</v>
+        <v>1344</v>
       </c>
       <c r="C261" t="n">
-        <v>113</v>
+        <v>433</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>LYR01O</t>
+          <t>MAD04O</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1344</v>
+        <v>600</v>
       </c>
       <c r="C262" t="n">
-        <v>433</v>
+        <v>241</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MAD04O</t>
+          <t>MEC02O</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C263" t="n">
-        <v>241</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MEC02O</t>
+          <t>MED02O</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C264" t="n">
-        <v>1456</v>
+        <v>640</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MED02O</t>
+          <t>MET07O</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C265" t="n">
-        <v>640</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MET07O</t>
+          <t>MID01O</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="C266" t="n">
-        <v>3138</v>
+        <v>737</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MID01O</t>
+          <t>MIN08O</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1500</v>
+        <v>120</v>
       </c>
       <c r="C267" t="n">
-        <v>737</v>
+        <v>25</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MIN08O</t>
+          <t>MIR04O</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C268" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MIR04O</t>
+          <t>MIY01O</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>100</v>
+        <v>5040</v>
       </c>
       <c r="C269" t="n">
-        <v>47</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MIY01O</t>
+          <t>MIY02O</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>5040</v>
+        <v>180</v>
       </c>
       <c r="C270" t="n">
-        <v>1410</v>
+        <v>98</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MIY02O</t>
+          <t>MOP01O</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>180</v>
+        <v>10080</v>
       </c>
       <c r="C271" t="n">
-        <v>98</v>
+        <v>4808</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MOP01O</t>
+          <t>MUL01O</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>10080</v>
+        <v>60</v>
       </c>
       <c r="C272" t="n">
-        <v>4808</v>
+        <v>87</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MUL01O</t>
+          <t>MYC05O</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="C273" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MYC05O</t>
+          <t>MYF01O</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>600</v>
+        <v>1680</v>
       </c>
       <c r="C274" t="n">
-        <v>148</v>
+        <v>89</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MYF01O</t>
+          <t>NAP04O</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1680</v>
+        <v>500</v>
       </c>
       <c r="C275" t="n">
-        <v>89</v>
+        <v>420</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>NAP04O</t>
+          <t>NAV05O</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="C276" t="n">
-        <v>420</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>NAV05O</t>
+          <t>NEB01O</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>5</v>
+        <v>1120</v>
       </c>
       <c r="C277" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>NEB01O</t>
+          <t>NEO05O</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1120</v>
+        <v>300</v>
       </c>
       <c r="C278" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>NEO05O</t>
+          <t>NER01O</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="C279" t="n">
-        <v>18</v>
+        <v>-97</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>NER01O</t>
+          <t>NEU01O</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="C280" t="n">
-        <v>-97</v>
+        <v>578</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>NEU01O</t>
+          <t>NEU03O</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="C281" t="n">
-        <v>578</v>
+        <v>825</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NEU03O</t>
+          <t>NEX01O</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1800</v>
+        <v>980</v>
       </c>
       <c r="C282" t="n">
-        <v>825</v>
+        <v>335</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>NEX01O</t>
+          <t>NIF01O</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>980</v>
+        <v>840</v>
       </c>
       <c r="C283" t="n">
-        <v>335</v>
+        <v>378</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>NIF01O</t>
+          <t>NOR07O</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>840</v>
+        <v>3360</v>
       </c>
       <c r="C284" t="n">
-        <v>378</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>NOR07O</t>
+          <t>NYS01O</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>3360</v>
+        <v>4000</v>
       </c>
       <c r="C285" t="n">
-        <v>1578</v>
+        <v>601</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>NYS01O</t>
+          <t>OFE01O</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>4000</v>
+        <v>360</v>
       </c>
       <c r="C286" t="n">
-        <v>601</v>
+        <v>172</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OFE01O</t>
+          <t>OLA01O</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="C287" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OLA01O</t>
+          <t>OLM03O</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>840</v>
+        <v>336</v>
       </c>
       <c r="C288" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>OLM03O</t>
+          <t>PAN01O</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>336</v>
+        <v>4200</v>
       </c>
       <c r="C289" t="n">
-        <v>143</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PAN01O</t>
+          <t>PAR08O</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>4200</v>
+        <v>140</v>
       </c>
       <c r="C290" t="n">
-        <v>1262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PAR08O</t>
+          <t>PEN01O</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="C291" t="n">
-        <v>45</v>
+        <v>462</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PEN01O</t>
+          <t>PEN02O</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="C292" t="n">
-        <v>462</v>
+        <v>39</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PEN02O</t>
+          <t>PIC03O</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="C293" t="n">
-        <v>39</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>PIC03O</t>
+          <t>PLA02O</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="C294" t="n">
-        <v>1170</v>
+        <v>413</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PLA02O</t>
+          <t>PLA03O</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>540</v>
+        <v>4032</v>
       </c>
       <c r="C295" t="n">
-        <v>413</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>PLA03O</t>
+          <t>PLE02O</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>4032</v>
+        <v>500</v>
       </c>
       <c r="C296" t="n">
-        <v>1117</v>
+        <v>445</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PLE02O</t>
+          <t>PRA01O</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C297" t="n">
-        <v>445</v>
+        <v>54</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>PRA01O</t>
+          <t>PRA02O</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="C298" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>PRA02O</t>
+          <t>PRO10O</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>60</v>
+        <v>952</v>
       </c>
       <c r="C299" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PRO10O</t>
+          <t>PRO15O</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>952</v>
+        <v>500</v>
       </c>
       <c r="C300" t="n">
-        <v>89</v>
+        <v>802</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PRO15O</t>
+          <t>PRO17O</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C301" t="n">
-        <v>802</v>
+        <v>186</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PRO17O</t>
+          <t>PRO20O</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="C302" t="n">
-        <v>186</v>
+        <v>575</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>PRO20O</t>
+          <t>PRO31O</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C303" t="n">
-        <v>575</v>
+        <v>670</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>PRO31O</t>
+          <t>QTE01O</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3000</v>
+        <v>140</v>
       </c>
       <c r="C304" t="n">
-        <v>670</v>
+        <v>54</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>QTE01O</t>
+          <t>RAS01O</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>140</v>
+        <v>3000</v>
       </c>
       <c r="C305" t="n">
-        <v>54</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>RAS01O</t>
+          <t>REL03O</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="C306" t="n">
-        <v>1227</v>
+        <v>489</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>REL03O</t>
+          <t>REV02O</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="C307" t="n">
-        <v>489</v>
+        <v>26</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>REV02O</t>
+          <t>REX01O</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C308" t="n">
-        <v>26</v>
+        <v>181</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>REX01O</t>
+          <t>RHY01O</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>180</v>
+        <v>1680</v>
       </c>
       <c r="C309" t="n">
-        <v>181</v>
+        <v>477</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>RHY01O</t>
+          <t>SAL01O</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>1680</v>
+        <v>1000</v>
       </c>
       <c r="C310" t="n">
-        <v>477</v>
+        <v>449</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SAL01O</t>
+          <t>SAL02O</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>1000</v>
       </c>
       <c r="C311" t="n">
-        <v>449</v>
+        <v>714</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SAL02O</t>
+          <t>SAM01O</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="C312" t="n">
-        <v>714</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SAM01O</t>
+          <t>SER03O</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>10</v>
+        <v>1800</v>
       </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>874</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SER03O</t>
+          <t>SER05O</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1800</v>
+        <v>360</v>
       </c>
       <c r="C314" t="n">
-        <v>874</v>
+        <v>234</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SER05O</t>
+          <t>SER09O</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>234</v>
+        <v>186</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SER09O</t>
+          <t>SET02O</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C316" t="n">
-        <v>186</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SET02O</t>
+          <t>SEV03O</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>17</v>
+        <v>-3060</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SEV03O</t>
+          <t>SIG01O</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C318" t="n">
-        <v>-3060</v>
+        <v>923</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>SIG01O</t>
+          <t>SIN15O</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>1000</v>
+        <v>224</v>
       </c>
       <c r="C319" t="n">
-        <v>923</v>
+        <v>124</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>SIN15O</t>
+          <t>SIN20O</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="C320" t="n">
-        <v>124</v>
+        <v>230</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SIN20O</t>
+          <t>SIR01O</t>
         </is>
       </c>
       <c r="B321" t="n">
         <v>300</v>
       </c>
       <c r="C321" t="n">
-        <v>230</v>
+        <v>495</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SIR01O</t>
+          <t>SLA01O</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="C322" t="n">
-        <v>495</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SLA01O</t>
+          <t>SOD05O</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="C323" t="n">
-        <v>1345</v>
+        <v>641</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SOD05O</t>
+          <t>SOL01O</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C324" t="n">
-        <v>641</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>SOL01O</t>
+          <t>SOL08O</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="C325" t="n">
-        <v>1185</v>
+        <v>248</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>SOL08O</t>
+          <t>STA05O</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="C326" t="n">
-        <v>248</v>
+        <v>449</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>STA05O</t>
+          <t>STR01O</t>
         </is>
       </c>
       <c r="B327" t="n">
         <v>2000</v>
       </c>
       <c r="C327" t="n">
-        <v>449</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>STR01O</t>
+          <t>SYM01O</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2000</v>
+        <v>56</v>
       </c>
       <c r="C328" t="n">
-        <v>1842</v>
+        <v>26</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SYM01O</t>
+          <t>TAG02O</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C329" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>TAG02O</t>
+          <t>TAI01O</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C330" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>TAI01O</t>
+          <t>TAK01O</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>80</v>
+        <v>4200</v>
       </c>
       <c r="C331" t="n">
-        <v>22</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TAK01O</t>
+          <t>TAM07O</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>4200</v>
+        <v>840</v>
       </c>
       <c r="C332" t="n">
-        <v>1396</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TAM07O</t>
+          <t>TEM02O</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>840</v>
+        <v>60</v>
       </c>
       <c r="C333" t="n">
-        <v>1154</v>
+        <v>18</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>TEM02O</t>
+          <t>TEM03O</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C334" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>TEM03O</t>
+          <t>THO01O</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="C335" t="n">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>THO01O</t>
+          <t>THR01O</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="C336" t="n">
-        <v>223</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>THR01O</t>
+          <t>TRA01O</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>20000</v>
+        <v>1350</v>
       </c>
       <c r="C337" t="n">
-        <v>6323</v>
+        <v>460</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TRA01O</t>
+          <t>TRA03O</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>1350</v>
+        <v>4000</v>
       </c>
       <c r="C338" t="n">
-        <v>460</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TRA03O</t>
+          <t>TRA14O</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>4000</v>
+        <v>480</v>
       </c>
       <c r="C339" t="n">
-        <v>1127</v>
+        <v>170</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TRA14O</t>
+          <t>TRI08O</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="C340" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>TRI08O</t>
+          <t>TS101O</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="C341" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TS101O</t>
+          <t>URI02O</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>70</v>
+        <v>560</v>
       </c>
       <c r="C342" t="n">
-        <v>212</v>
+        <v>238</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>URI02O</t>
+          <t>URO05O</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="C343" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>URO05O</t>
+          <t>UTA01O</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="C344" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>UTA01O</t>
+          <t>UWA01O</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="C345" t="n">
-        <v>237</v>
+        <v>441</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>UWA01O</t>
+          <t>UWA02O</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C346" t="n">
-        <v>441</v>
+        <v>82</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>UWA02O</t>
+          <t>VAN04O</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C347" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>VAN04O</t>
+          <t>VEM01O</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C348" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>VEM01O</t>
+          <t>VER01O</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>360</v>
+        <v>56</v>
       </c>
       <c r="C349" t="n">
-        <v>182</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>VER01O</t>
+          <t>VIM01O</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>56</v>
+        <v>504</v>
       </c>
       <c r="C350" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>VIM01O</t>
+          <t>VOL01O</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>504</v>
+        <v>2000</v>
       </c>
       <c r="C351" t="n">
-        <v>165</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>VOL01O</t>
+          <t>WEL03O</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="C352" t="n">
-        <v>1690</v>
+        <v>473</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>WEL03O</t>
+          <t>WIT01O</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="C353" t="n">
-        <v>473</v>
+        <v>54</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>WIT01O</t>
+          <t>XAL01O</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C354" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>XAL01O</t>
+          <t>XAN03O</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="C355" t="n">
-        <v>14</v>
+        <v>590</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>XAN03O</t>
+          <t>XAR02O</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="C356" t="n">
-        <v>590</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>XAR02O</t>
+          <t>YOU01O</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="C357" t="n">
-        <v>3</v>
+        <v>198</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>YOU01O</t>
+          <t>ZAN02O</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="C358" t="n">
-        <v>198</v>
+        <v>728</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ZAN02O</t>
+          <t>ZAP01O</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="C359" t="n">
-        <v>728</v>
+        <v>402</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ZAP01O</t>
+          <t>ZCO01O</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C360" t="n">
-        <v>402</v>
+        <v>931</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ZCO01O</t>
+          <t>ZIT01O</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3000</v>
+        <v>72</v>
       </c>
       <c r="C361" t="n">
-        <v>931</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ZIT01O</t>
+          <t>ZOL02O</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>72</v>
+        <v>1120</v>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>549</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ZOL02O</t>
+          <t>ZYP02O</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>1120</v>
+        <v>560</v>
       </c>
       <c r="C363" t="n">
-        <v>549</v>
+        <v>114</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ZYP02O</t>
+          <t>ZYV01O</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>560</v>
+        <v>60</v>
       </c>
       <c r="C364" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ZYV01O</t>
+          <t>ALC02E</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C365" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ALC02E</t>
+          <t>ALC04E</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="C366" t="n">
-        <v>139</v>
+        <v>17</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ALC04E</t>
+          <t>BER05E</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C367" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>BER05E</t>
+          <t>BIS02E</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="C368" t="n">
-        <v>10</v>
+        <v>448</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>BIS02E</t>
+          <t>BRE01E</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="C369" t="n">
-        <v>448</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>BRE01E</t>
+          <t>CAL01E</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C370" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CAL01E</t>
+          <t>CBO01E</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C371" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CBO01E</t>
+          <t>CHA01E</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="C372" t="n">
-        <v>7</v>
+        <v>166</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CHA01E</t>
+          <t>CHL02E</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="C373" t="n">
-        <v>166</v>
+        <v>9</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CHL02E</t>
+          <t>CIV01E</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="C374" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CIV01E</t>
+          <t>CLO02E</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="C375" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CLO02E</t>
+          <t>CLO04E</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CLO04E</t>
+          <t>COM02E</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1</v>
+        <v>8640</v>
       </c>
       <c r="C377" t="n">
-        <v>0</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>COM02E</t>
+          <t>DIF01E</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>8640</v>
+        <v>12</v>
       </c>
       <c r="C378" t="n">
-        <v>2697</v>
+        <v>6</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DIF01E</t>
+          <t>EAR01E</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C379" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>EAR01E</t>
+          <t>EAS02E</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C380" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>EAS02E</t>
+          <t>ENO01E</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C381" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ENO01E</t>
+          <t>EVA01E</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="C382" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>EVA01E</t>
+          <t>FUC03E</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>216</v>
+        <v>30</v>
       </c>
       <c r="C383" t="n">
-        <v>109</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>FUC03E</t>
+          <t>FUS02E</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="C384" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>FUS02E</t>
+          <t>IPR02E</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="C385" t="n">
-        <v>19</v>
+        <v>289</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>IPR02E</t>
+          <t>KAR01E</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="C386" t="n">
-        <v>289</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>KAR01E</t>
+          <t>KET01E</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C387" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>KET01E</t>
+          <t>LID01E</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C388" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>LID01E</t>
+          <t>LOM02E</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C389" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>LOM02E</t>
+          <t>MES01E</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="C390" t="n">
-        <v>16</v>
+        <v>327</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>MES01E</t>
+          <t>NEO01E</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="C391" t="n">
-        <v>327</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>NEO01E</t>
+          <t>NIN02E</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="C392" t="n">
-        <v>-10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>NIN02E</t>
+          <t>OPT02E</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C393" t="n">
-        <v>52</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>OPT02E</t>
+          <t>PAR08E</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C394" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>PAR08E</t>
+          <t>SAL03E</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="C395" t="n">
-        <v>12</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>SAL03E</t>
+          <t>SER09E</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="C396" t="n">
-        <v>1379</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>SER09E</t>
+          <t>SIL03E</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>SIL03E</t>
+          <t>SIL06E</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C398" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>SIL06E</t>
+          <t>SIN11E</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C399" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>SIN11E</t>
+          <t>SPI05E</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C400" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SPI05E</t>
+          <t>TOP02E</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C401" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>TOP02E</t>
+          <t>TOR01E</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C402" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TOR01E</t>
+          <t>URE04E</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C403" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>URE04E</t>
+          <t>VID01E</t>
         </is>
       </c>
       <c r="B404" t="n">
         <v>10</v>
       </c>
       <c r="C404" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>VID01E</t>
+          <t>VIG01E</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C405" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>VIG01E</t>
+          <t>VIM01E</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C406" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>VIM01E</t>
+          <t>VOR02E</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C407" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>VOR02E</t>
+          <t>VOR03E</t>
         </is>
       </c>
       <c r="B408" t="n">
         <v>100</v>
       </c>
       <c r="C408" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>VOR03E</t>
+          <t>XYJ01E</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="C409" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>XYJ01E</t>
+          <t>ZAL02E</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="C410" t="n">
-        <v>97</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ZAL02E</t>
+          <t>ZIN04E</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C411" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ZIN04E</t>
+          <t>CHE01S</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C412" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CHE01S</t>
+          <t>FLU01S</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C413" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>FLU01S</t>
+          <t>SCR01S</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>8</v>
+        <v>480</v>
       </c>
       <c r="C414" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SCR01S</t>
-        </is>
-      </c>
-      <c r="B415" t="n">
-        <v>480</v>
-      </c>
-      <c r="C415" t="n">
         <v>162</v>
       </c>
     </row>
